--- a/バージョン管理表.xlsx
+++ b/バージョン管理表.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OpenCode\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3E9A0FD-7820-4F64-A7B7-CDF68CAAFD38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="30525" windowHeight="16980"/>
+    <workbookView xWindow="14325" yWindow="1665" windowWidth="33255" windowHeight="18840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="統合ソフト" sheetId="4" r:id="rId1"/>
@@ -863,16 +869,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
-    <numFmt numFmtId="177" formatCode="0.000000_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="178" formatCode="0.00_ "/>
+    <numFmt numFmtId="179" formatCode="0.000000_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -887,163 +889,32 @@
       <charset val="134"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1058,198 +929,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.149632251960814"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="0" tint="-0.14960173345133823"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -1272,254 +957,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="50">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1545,75 +988,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" quotePrefix="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" quotePrefix="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="50">
+  <cellStyles count="2">
+    <cellStyle name="標準 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
-    <cellStyle name="標準 2" xfId="49"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1871,17 +1269,17 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:G87"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="15.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
     <col min="4" max="4" width="15.75" customWidth="1"/>
     <col min="5" max="5" width="24.75" customWidth="1"/>
     <col min="6" max="6" width="62.75" customWidth="1"/>
@@ -1908,97 +1306,109 @@
       </c>
     </row>
     <row r="4" spans="2:7">
-      <c r="B4" s="13">
+      <c r="B4" s="12">
         <v>45170</v>
       </c>
-      <c r="C4" s="14">
+      <c r="C4" s="13">
         <f>SOC!C4</f>
-        <v>0.00011</v>
-      </c>
-      <c r="D4" s="17" t="str">
+        <v>1.1E-4</v>
+      </c>
+      <c r="D4" s="16" t="str">
         <f>MCU!C4</f>
         <v>00.01</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="15"/>
+      <c r="F4" s="14">
+        <v>11</v>
+      </c>
       <c r="G4" s="6"/>
     </row>
     <row r="5" spans="2:7">
-      <c r="B5" s="13">
+      <c r="B5" s="12">
         <v>45225</v>
       </c>
-      <c r="C5" s="14">
+      <c r="C5" s="13">
         <f>SOC!C5</f>
-        <v>0.02041</v>
-      </c>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
-      <c r="F5" s="15"/>
+        <v>2.0410000000000001E-2</v>
+      </c>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14">
+        <v>22</v>
+      </c>
       <c r="G5" s="6"/>
     </row>
     <row r="6" spans="2:7">
-      <c r="B6" s="13">
+      <c r="B6" s="12">
         <v>45229</v>
       </c>
-      <c r="C6" s="14">
+      <c r="C6" s="13">
         <f>SOC!C6</f>
-        <v>0.02046</v>
-      </c>
-      <c r="D6" s="15"/>
-      <c r="E6" s="15"/>
-      <c r="F6" s="15"/>
+        <v>2.0459999999999999E-2</v>
+      </c>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
+      <c r="F6" s="14">
+        <v>33</v>
+      </c>
       <c r="G6" s="6"/>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" s="5">
         <v>45230</v>
       </c>
-      <c r="C7" s="12"/>
-      <c r="D7" s="18" t="str">
+      <c r="C7" s="11"/>
+      <c r="D7" s="17" t="str">
         <f>MCU!C5</f>
         <v>21.00</v>
       </c>
       <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
+      <c r="F7" s="6">
+        <v>44</v>
+      </c>
       <c r="G7" s="6"/>
     </row>
     <row r="8" spans="2:7">
       <c r="B8" s="5">
         <v>45231</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <f>SOC!C7</f>
-        <v>0.02051</v>
+        <v>2.051E-2</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
+      <c r="F8" s="6">
+        <v>55</v>
+      </c>
       <c r="G8" s="6"/>
     </row>
     <row r="9" spans="2:7">
       <c r="B9" s="5">
         <v>45236</v>
       </c>
-      <c r="C9" s="12"/>
-      <c r="D9" s="18" t="str">
+      <c r="C9" s="11"/>
+      <c r="D9" s="17" t="str">
         <f>MCU!C6</f>
         <v>00.01</v>
       </c>
       <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
+      <c r="F9" s="6">
+        <v>66</v>
+      </c>
       <c r="G9" s="6"/>
     </row>
     <row r="10" spans="2:7">
       <c r="B10" s="5">
         <v>45244</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <f>SOC!C8</f>
-        <v>0.0207</v>
-      </c>
-      <c r="D10" s="18" t="str">
+        <v>2.07E-2</v>
+      </c>
+      <c r="D10" s="17" t="str">
         <f>MCU!C7</f>
         <v>20.49</v>
       </c>
@@ -2010,8 +1420,8 @@
       <c r="B11" s="5">
         <v>45250</v>
       </c>
-      <c r="C11" s="12"/>
-      <c r="D11" s="18" t="str">
+      <c r="C11" s="11"/>
+      <c r="D11" s="17" t="str">
         <f>MCU!C8</f>
         <v>20.55</v>
       </c>
@@ -2023,8 +1433,8 @@
       <c r="B12" s="5">
         <v>45264</v>
       </c>
-      <c r="C12" s="12"/>
-      <c r="D12" s="18" t="str">
+      <c r="C12" s="11"/>
+      <c r="D12" s="17" t="str">
         <f>MCU!C9</f>
         <v>30.02</v>
       </c>
@@ -2036,11 +1446,11 @@
       <c r="B13" s="5">
         <v>45271</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="11">
         <f>SOC!C9</f>
-        <v>0.03016</v>
-      </c>
-      <c r="D13" s="18" t="str">
+        <v>3.0159999999999999E-2</v>
+      </c>
+      <c r="D13" s="17" t="str">
         <f>MCU!C10</f>
         <v>30.13</v>
       </c>
@@ -2056,11 +1466,11 @@
       <c r="B14" s="5">
         <v>45279</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <f>SOC!C10</f>
-        <v>0.0303</v>
-      </c>
-      <c r="D14" s="18" t="str">
+        <v>3.0300000000000001E-2</v>
+      </c>
+      <c r="D14" s="17" t="str">
         <f>MCU!C11</f>
         <v>30.20</v>
       </c>
@@ -2076,9 +1486,9 @@
       <c r="B15" s="5">
         <v>45282</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="11">
         <f>SOC!C11</f>
-        <v>0.030331</v>
+        <v>3.0331E-2</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -2087,19 +1497,19 @@
       </c>
       <c r="G15" s="6"/>
     </row>
-    <row r="16" ht="16.5" spans="2:7">
+    <row r="16" spans="2:7" ht="16.5">
       <c r="B16" s="5">
         <v>45306</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <f>SOC!C12</f>
-        <v>0.03066</v>
-      </c>
-      <c r="D16" s="18" t="str">
+        <v>3.066E-2</v>
+      </c>
+      <c r="D16" s="17" t="str">
         <f>MCU!C12</f>
         <v>30.48</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="15" t="s">
         <v>9</v>
       </c>
       <c r="F16" s="6" t="s">
@@ -2111,11 +1521,11 @@
       <c r="B17" s="5">
         <v>45348</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="11">
         <f>SOC!C13</f>
-        <v>0.03126</v>
-      </c>
-      <c r="D17" s="18" t="str">
+        <v>3.1260000000000003E-2</v>
+      </c>
+      <c r="D17" s="17" t="str">
         <f>MCU!C13</f>
         <v>30.90</v>
       </c>
@@ -2132,9 +1542,9 @@
       <c r="B18" s="5">
         <v>45357</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <f>SOC!C14</f>
-        <v>0.031261</v>
+        <v>3.1260999999999997E-2</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>9</v>
@@ -2149,11 +1559,11 @@
       <c r="B19" s="5">
         <v>45369</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="11">
         <f>SOC!C15</f>
-        <v>0.03156</v>
-      </c>
-      <c r="D19" s="18" t="str">
+        <v>3.1559999999999998E-2</v>
+      </c>
+      <c r="D19" s="17" t="str">
         <f>MCU!C14</f>
         <v>31.11</v>
       </c>
@@ -2170,11 +1580,11 @@
       <c r="B20" s="5">
         <v>45383</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <f>SOC!C16</f>
-        <v>0.0317</v>
-      </c>
-      <c r="D20" s="18" t="str">
+        <v>3.1699999999999999E-2</v>
+      </c>
+      <c r="D20" s="17" t="str">
         <f>MCU!C15</f>
         <v>31.21</v>
       </c>
@@ -2189,11 +1599,11 @@
       <c r="B21" s="5">
         <v>45397</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <f>SOC!C17</f>
-        <v>0.0319</v>
-      </c>
-      <c r="D21" s="18" t="str">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="D21" s="17" t="str">
         <f>MCU!C16</f>
         <v>31.35</v>
       </c>
@@ -2208,11 +1618,11 @@
       <c r="B22" s="5">
         <v>45406</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="11">
         <f>SOC!C18</f>
-        <v>0.03203</v>
-      </c>
-      <c r="D22" s="18" t="str">
+        <v>3.2030000000000003E-2</v>
+      </c>
+      <c r="D22" s="17" t="str">
         <f>MCU!C17</f>
         <v>31.42</v>
       </c>
@@ -2227,11 +1637,11 @@
       <c r="B23" s="5">
         <v>45407</v>
       </c>
-      <c r="C23" s="12">
+      <c r="C23" s="11">
         <f>SOC!C19</f>
-        <v>0.032031</v>
-      </c>
-      <c r="D23" s="18" t="str">
+        <v>3.2030999999999997E-2</v>
+      </c>
+      <c r="D23" s="17" t="str">
         <f>MCU!C17</f>
         <v>31.42</v>
       </c>
@@ -2246,11 +1656,11 @@
       <c r="B24" s="5">
         <v>45411</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="11">
         <f>SOC!C20</f>
-        <v>0.0321</v>
-      </c>
-      <c r="D24" s="18" t="str">
+        <v>3.2099999999999997E-2</v>
+      </c>
+      <c r="D24" s="17" t="str">
         <f>MCU!C18</f>
         <v>31.50</v>
       </c>
@@ -2265,11 +1675,11 @@
       <c r="B25" s="5">
         <v>45432</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="11">
         <f>VLOOKUP(B25,SOC!B:D,2,FALSE)</f>
         <v>0.04</v>
       </c>
-      <c r="D25" s="18" t="str">
+      <c r="D25" s="17" t="str">
         <f>VLOOKUP(B25,MCU!B:D,2,FALSE)</f>
         <v>40.01</v>
       </c>
@@ -2284,11 +1694,11 @@
       <c r="B26" s="5">
         <v>45446</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="11">
         <f>VLOOKUP(B26,SOC!B:D,2,FALSE)</f>
-        <v>0.0402</v>
-      </c>
-      <c r="D26" s="18" t="str">
+        <v>4.02E-2</v>
+      </c>
+      <c r="D26" s="17" t="str">
         <f>VLOOKUP(B26,MCU!B:D,2,FALSE)</f>
         <v>40.18</v>
       </c>
@@ -2303,11 +1713,11 @@
       <c r="B27" s="5">
         <v>45460</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="11">
         <f>VLOOKUP(B27,SOC!B:D,2,FALSE)</f>
-        <v>0.0404</v>
-      </c>
-      <c r="D27" s="18" t="str">
+        <v>4.0399999999999998E-2</v>
+      </c>
+      <c r="D27" s="17" t="str">
         <f>VLOOKUP(B27,MCU!B:D,2,FALSE)</f>
         <v>40.28</v>
       </c>
@@ -2322,11 +1732,11 @@
       <c r="B28" s="5">
         <v>45474</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="11">
         <f>VLOOKUP(B28,SOC!B:D,2,FALSE)</f>
-        <v>0.0406</v>
-      </c>
-      <c r="D28" s="18" t="str">
+        <v>4.0599999999999997E-2</v>
+      </c>
+      <c r="D28" s="17" t="str">
         <f>VLOOKUP(B28,MCU!B:D,2,FALSE)</f>
         <v>40.42</v>
       </c>
@@ -2341,11 +1751,11 @@
       <c r="B29" s="5">
         <v>45488</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="11">
         <f>VLOOKUP(B29,SOC!B:D,2,FALSE)</f>
-        <v>0.0408</v>
-      </c>
-      <c r="D29" s="18" t="str">
+        <v>4.0800000000000003E-2</v>
+      </c>
+      <c r="D29" s="17" t="str">
         <f>VLOOKUP(B29,MCU!B:D,2,FALSE)</f>
         <v>40.56</v>
       </c>
@@ -2360,7 +1770,7 @@
       <c r="B30" s="5">
         <v>45492</v>
       </c>
-      <c r="C30" s="12" t="str">
+      <c r="C30" s="11" t="str">
         <f>VLOOKUP(B30,SOC!B:D,2,FALSE)</f>
         <v>↑と同様</v>
       </c>
@@ -2379,11 +1789,11 @@
       <c r="B31" s="5">
         <v>45502</v>
       </c>
-      <c r="C31" s="12">
+      <c r="C31" s="11">
         <f>VLOOKUP(B31,SOC!B:D,2,FALSE)</f>
-        <v>0.041</v>
-      </c>
-      <c r="D31" s="18" t="str">
+        <v>4.1000000000000002E-2</v>
+      </c>
+      <c r="D31" s="17" t="str">
         <f>VLOOKUP(B31,MCU!B:D,2,FALSE)</f>
         <v>40.71</v>
       </c>
@@ -2398,9 +1808,9 @@
       <c r="B32" s="5">
         <v>45510</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="11">
         <f>VLOOKUP(B32,SOC!B:D,2,FALSE)</f>
-        <v>0.0411</v>
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="D32" s="6" t="str">
         <f>VLOOKUP(B32,MCU!B:D,2,FALSE)</f>
@@ -2421,11 +1831,11 @@
       <c r="B33" s="5">
         <v>45523</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="11">
         <f>VLOOKUP(B33,SOC!B:D,2,FALSE)</f>
-        <v>0.0413</v>
-      </c>
-      <c r="D33" s="18" t="str">
+        <v>4.1300000000000003E-2</v>
+      </c>
+      <c r="D33" s="17" t="str">
         <f>VLOOKUP(B33,MCU!B:D,2,FALSE)</f>
         <v>40.91</v>
       </c>
@@ -2440,11 +1850,11 @@
       <c r="B34" s="5">
         <v>45534</v>
       </c>
-      <c r="C34" s="12">
+      <c r="C34" s="11">
         <f>VLOOKUP(B34,SOC!B:D,2,FALSE)</f>
-        <v>0.0411</v>
-      </c>
-      <c r="D34" s="18" t="str">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="D34" s="17" t="str">
         <f>VLOOKUP(B34,MCU!B:D,2,FALSE)</f>
         <v>40.72</v>
       </c>
@@ -2459,11 +1869,11 @@
       <c r="B35" s="5">
         <v>45537</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="11">
         <f>VLOOKUP(B35,SOC!B:D,2,FALSE)</f>
-        <v>0.0415</v>
-      </c>
-      <c r="D35" s="18" t="str">
+        <v>4.1500000000000002E-2</v>
+      </c>
+      <c r="D35" s="17" t="str">
         <f>VLOOKUP(B35,MCU!B:D,2,FALSE)</f>
         <v>41.05</v>
       </c>
@@ -2478,11 +1888,11 @@
       <c r="B36" s="5">
         <v>45553</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="11">
         <f>VLOOKUP(B36,SOC!B:D,2,FALSE)</f>
-        <v>0.0417</v>
-      </c>
-      <c r="D36" s="18" t="str">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="D36" s="17" t="str">
         <f>VLOOKUP(B36,MCU!B:D,2,FALSE)</f>
         <v>41.19</v>
       </c>
@@ -2497,11 +1907,11 @@
       <c r="B37" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="11">
         <f>VLOOKUP(B37,SOC!B:D,2,FALSE)</f>
-        <v>0.04171</v>
-      </c>
-      <c r="D37" s="18" t="str">
+        <v>4.1709999999999997E-2</v>
+      </c>
+      <c r="D37" s="17" t="str">
         <f>VLOOKUP(B37,MCU!B:D,2,FALSE)</f>
         <v>41.19</v>
       </c>
@@ -2516,11 +1926,11 @@
       <c r="B38" s="5">
         <v>45554</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="11">
         <f>VLOOKUP(B38,SOC!B:D,2,FALSE)</f>
-        <v>0.0417</v>
-      </c>
-      <c r="D38" s="18" t="str">
+        <v>4.1700000000000001E-2</v>
+      </c>
+      <c r="D38" s="17" t="str">
         <f>VLOOKUP(B38,MCU!B:D,2,FALSE)</f>
         <v>41.20</v>
       </c>
@@ -2534,11 +1944,11 @@
       <c r="B39" s="5">
         <v>45555</v>
       </c>
-      <c r="C39" s="12">
+      <c r="C39" s="11">
         <f>VLOOKUP(B39,SOC!B:D,2,FALSE)</f>
-        <v>0.0411</v>
-      </c>
-      <c r="D39" s="18" t="str">
+        <v>4.1099999999999998E-2</v>
+      </c>
+      <c r="D39" s="17" t="str">
         <f>VLOOKUP(B39,MCU!B:D,2,FALSE)</f>
         <v>40.73</v>
       </c>
@@ -2556,11 +1966,11 @@
       <c r="B40" s="5">
         <v>45564</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="11">
         <f>VLOOKUP(B40,SOC!B:D,2,FALSE)</f>
-        <v>0.0419</v>
-      </c>
-      <c r="D40" s="18" t="str">
+        <v>4.19E-2</v>
+      </c>
+      <c r="D40" s="17" t="str">
         <f>VLOOKUP(B40,MCU!B:D,2,FALSE)</f>
         <v>41.36</v>
       </c>
@@ -2577,11 +1987,11 @@
       <c r="B41" s="5">
         <v>45579</v>
       </c>
-      <c r="C41" s="12">
+      <c r="C41" s="11">
         <f>VLOOKUP(B41,SOC!B:D,2,FALSE)</f>
-        <v>0.0421</v>
-      </c>
-      <c r="D41" s="18" t="str">
+        <v>4.2099999999999999E-2</v>
+      </c>
+      <c r="D41" s="17" t="str">
         <f>VLOOKUP(B41,MCU!B:D,2,FALSE)</f>
         <v>41.48</v>
       </c>
@@ -2595,11 +2005,11 @@
       <c r="B42" s="5">
         <v>45593</v>
       </c>
-      <c r="C42" s="12">
+      <c r="C42" s="11">
         <f>VLOOKUP(B42,SOC!B:D,2,FALSE)</f>
         <v>0.05</v>
       </c>
-      <c r="D42" s="18" t="str">
+      <c r="D42" s="17" t="str">
         <f>VLOOKUP(B42,MCU!B:D,2,FALSE)</f>
         <v>41.62</v>
       </c>
@@ -2616,11 +2026,11 @@
       <c r="B43" s="5">
         <v>45607</v>
       </c>
-      <c r="C43" s="12">
+      <c r="C43" s="11">
         <f>VLOOKUP(B43,SOC!B:D,2,FALSE)</f>
-        <v>0.0503</v>
-      </c>
-      <c r="D43" s="18" t="str">
+        <v>5.0299999999999997E-2</v>
+      </c>
+      <c r="D43" s="17" t="str">
         <f>VLOOKUP(B43,MCU!B:D,2,FALSE)</f>
         <v>41.75</v>
       </c>
@@ -2638,11 +2048,11 @@
       <c r="B44" s="5">
         <v>45621</v>
       </c>
-      <c r="C44" s="12">
+      <c r="C44" s="11">
         <f>VLOOKUP(B44,SOC!B:D,2,FALSE)</f>
-        <v>0.0505</v>
-      </c>
-      <c r="D44" s="18" t="str">
+        <v>5.0500000000000003E-2</v>
+      </c>
+      <c r="D44" s="17" t="str">
         <f>VLOOKUP(B44,MCU!B:D,2,FALSE)</f>
         <v>41.90</v>
       </c>
@@ -2661,11 +2071,11 @@
       <c r="B45" s="5">
         <v>45637</v>
       </c>
-      <c r="C45" s="12">
+      <c r="C45" s="11">
         <f>VLOOKUP(B45,SOC!B:D,2,FALSE)</f>
-        <v>0.0507</v>
-      </c>
-      <c r="D45" s="18" t="str">
+        <v>5.0700000000000002E-2</v>
+      </c>
+      <c r="D45" s="17" t="str">
         <f>VLOOKUP(B45,MCU!B:D,2,FALSE)</f>
         <v>42.07</v>
       </c>
@@ -2684,11 +2094,11 @@
       <c r="B46" s="5">
         <v>45660</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="11">
         <f>VLOOKUP(B46,SOC!B:D,2,FALSE)</f>
-        <v>0.0511</v>
-      </c>
-      <c r="D46" s="18" t="str">
+        <v>5.11E-2</v>
+      </c>
+      <c r="D46" s="17" t="str">
         <f>VLOOKUP(B46,MCU!B:D,2,FALSE)</f>
         <v>42.31</v>
       </c>
@@ -2703,11 +2113,11 @@
       <c r="B47" s="5">
         <v>45679</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="11">
         <f>VLOOKUP(B47,SOC!B:D,2,FALSE)</f>
-        <v>0.0513</v>
-      </c>
-      <c r="D47" s="18" t="str">
+        <v>5.1299999999999998E-2</v>
+      </c>
+      <c r="D47" s="17" t="str">
         <f>VLOOKUP(B47,MCU!B:D,2,FALSE)</f>
         <v>42.45</v>
       </c>
@@ -2722,11 +2132,11 @@
       <c r="B48" s="5">
         <v>45698</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="11">
         <f>VLOOKUP(B48,SOC!B:D,2,FALSE)</f>
-        <v>0.0516</v>
-      </c>
-      <c r="D48" s="18" t="str">
+        <v>5.16E-2</v>
+      </c>
+      <c r="D48" s="17" t="str">
         <f>VLOOKUP(B48,MCU!B:D,2,FALSE)</f>
         <v>42.66</v>
       </c>
@@ -2742,11 +2152,11 @@
       <c r="B49" s="5">
         <v>45707</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="11">
         <f>VLOOKUP(B49,SOC!B:D,2,FALSE)</f>
-        <v>0.0517</v>
-      </c>
-      <c r="D49" s="18" t="str">
+        <v>5.1700000000000003E-2</v>
+      </c>
+      <c r="D49" s="17" t="str">
         <f>VLOOKUP(B49,MCU!B:D,2,FALSE)</f>
         <v>42.74</v>
       </c>
@@ -2763,11 +2173,11 @@
       <c r="B50" s="5">
         <v>45719</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="11">
         <f>VLOOKUP(B50,SOC!B:D,2,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="D50" s="18" t="str">
+      <c r="D50" s="17" t="str">
         <f>VLOOKUP(B50,MCU!B:D,2,FALSE)</f>
         <v>50.00</v>
       </c>
@@ -2786,11 +2196,11 @@
       <c r="B51" s="5">
         <v>45733</v>
       </c>
-      <c r="C51" s="12">
+      <c r="C51" s="11">
         <f>VLOOKUP(B51,SOC!B:D,2,FALSE)</f>
         <v>1.0001</v>
       </c>
-      <c r="D51" s="18" t="str">
+      <c r="D51" s="17" t="str">
         <f>VLOOKUP(B51,MCU!B:D,2,FALSE)</f>
         <v>50.01</v>
       </c>
@@ -2805,11 +2215,11 @@
       <c r="B52" s="5">
         <v>45754</v>
       </c>
-      <c r="C52" s="12">
+      <c r="C52" s="11">
         <f>VLOOKUP(B52,SOC!B:D,2,FALSE)</f>
         <v>1.0002</v>
       </c>
-      <c r="D52" s="18" t="str">
+      <c r="D52" s="17" t="str">
         <f>VLOOKUP(B52,MCU!B:D,2,FALSE)</f>
         <v>50.01</v>
       </c>
@@ -2824,11 +2234,11 @@
       <c r="B53" s="5">
         <v>45761</v>
       </c>
-      <c r="C53" s="12">
+      <c r="C53" s="11">
         <f>VLOOKUP(B53,SOC!B:D,2,FALSE)</f>
         <v>1.0003</v>
       </c>
-      <c r="D53" s="18" t="str">
+      <c r="D53" s="17" t="str">
         <f>VLOOKUP(B53,MCU!B:D,2,FALSE)</f>
         <v>50.02</v>
       </c>
@@ -2843,11 +2253,11 @@
       <c r="B54" s="5">
         <v>45777</v>
       </c>
-      <c r="C54" s="12">
+      <c r="C54" s="11">
         <f>VLOOKUP(B54,SOC!B:D,2,FALSE)</f>
         <v>1.0004</v>
       </c>
-      <c r="D54" s="18" t="str">
+      <c r="D54" s="17" t="str">
         <f>VLOOKUP(B54,MCU!B:D,2,FALSE)</f>
         <v>50.03</v>
       </c>
@@ -2862,11 +2272,11 @@
       <c r="B55" s="5">
         <v>45786</v>
       </c>
-      <c r="C55" s="12">
+      <c r="C55" s="11">
         <f>VLOOKUP(B55,SOC!B:D,2,FALSE)</f>
-        <v>1.0006</v>
-      </c>
-      <c r="D55" s="18" t="str">
+        <v>1.0005999999999999</v>
+      </c>
+      <c r="D55" s="17" t="str">
         <f>VLOOKUP(B55,MCU!B:D,2,FALSE)</f>
         <v>50.03</v>
       </c>
@@ -2885,11 +2295,11 @@
       <c r="B56" s="5">
         <v>45797</v>
       </c>
-      <c r="C56" s="12">
+      <c r="C56" s="11">
         <f>VLOOKUP(B56,SOC!B:D,2,FALSE)</f>
-        <v>1.0006</v>
-      </c>
-      <c r="D56" s="18" t="str">
+        <v>1.0005999999999999</v>
+      </c>
+      <c r="D56" s="17" t="str">
         <f>VLOOKUP(B56,MCU!B:D,2,FALSE)</f>
         <v>50.03</v>
       </c>
@@ -2906,11 +2316,11 @@
       <c r="B57" s="5">
         <v>45803</v>
       </c>
-      <c r="C57" s="12">
+      <c r="C57" s="11">
         <f>VLOOKUP(B57,SOC!B:D,2,FALSE)</f>
-        <v>1.0008</v>
-      </c>
-      <c r="D57" s="18" t="str">
+        <v>1.0007999999999999</v>
+      </c>
+      <c r="D57" s="17" t="str">
         <f>VLOOKUP(B57,MCU!B:D,2,FALSE)</f>
         <v>50.04</v>
       </c>
@@ -2925,11 +2335,11 @@
       <c r="B58" s="5">
         <v>45825</v>
       </c>
-      <c r="C58" s="12">
+      <c r="C58" s="11">
         <f>VLOOKUP(B58,SOC!B:D,2,FALSE)</f>
-        <v>1.0009</v>
-      </c>
-      <c r="D58" s="18" t="str">
+        <v>1.0008999999999999</v>
+      </c>
+      <c r="D58" s="17" t="str">
         <f>VLOOKUP(B58,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -2944,11 +2354,11 @@
       <c r="B59" s="5">
         <v>45826</v>
       </c>
-      <c r="C59" s="12">
+      <c r="C59" s="11">
         <f>VLOOKUP(B59,SOC!B:D,2,FALSE)</f>
-        <v>1.001</v>
-      </c>
-      <c r="D59" s="18" t="str">
+        <v>1.0009999999999999</v>
+      </c>
+      <c r="D59" s="17" t="str">
         <f>VLOOKUP(B59,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -2965,11 +2375,11 @@
       <c r="B60" s="5">
         <v>45838</v>
       </c>
-      <c r="C60" s="12">
+      <c r="C60" s="11">
         <f>VLOOKUP(B60,SOC!B:D,2,FALSE)</f>
-        <v>1.0011</v>
-      </c>
-      <c r="D60" s="18" t="str">
+        <v>1.0011000000000001</v>
+      </c>
+      <c r="D60" s="17" t="str">
         <f>VLOOKUP(B60,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -2984,11 +2394,11 @@
       <c r="B61" s="5">
         <v>45854</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="11">
         <f>VLOOKUP(B61,SOC!B:D,2,FALSE)</f>
-        <v>1.0012</v>
-      </c>
-      <c r="D61" s="18" t="str">
+        <v>1.0012000000000001</v>
+      </c>
+      <c r="D61" s="17" t="str">
         <f>VLOOKUP(B61,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -3003,11 +2413,11 @@
       <c r="B62" s="5">
         <v>45859</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="11">
         <f>VLOOKUP(B62,SOC!B:D,2,FALSE)</f>
-        <v>1.0013</v>
-      </c>
-      <c r="D62" s="18" t="str">
+        <v>1.0013000000000001</v>
+      </c>
+      <c r="D62" s="17" t="str">
         <f>VLOOKUP(B62,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -3026,11 +2436,11 @@
       <c r="B63" s="5">
         <v>45884</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="11">
         <f>VLOOKUP(B63,SOC!B:D,2,FALSE)</f>
-        <v>1.0014</v>
-      </c>
-      <c r="D63" s="18" t="str">
+        <v>1.0014000000000001</v>
+      </c>
+      <c r="D63" s="17" t="str">
         <f>VLOOKUP(B63,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -3047,11 +2457,11 @@
       <c r="B64" s="5">
         <v>45915</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="11">
         <f>VLOOKUP(B64,SOC!B:D,2,FALSE)</f>
-        <v>1.0015</v>
-      </c>
-      <c r="D64" s="18" t="str">
+        <v>1.0015000000000001</v>
+      </c>
+      <c r="D64" s="17" t="str">
         <f>VLOOKUP(B64,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -3066,11 +2476,11 @@
       <c r="B65" s="5">
         <v>45944</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="11">
         <f>VLOOKUP(B65,SOC!B:D,2,FALSE)</f>
         <v>1.0016</v>
       </c>
-      <c r="D65" s="18" t="str">
+      <c r="D65" s="17" t="str">
         <f>VLOOKUP(B65,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -3085,11 +2495,11 @@
       <c r="B66" s="5">
         <v>45950</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="11">
         <f>VLOOKUP(B66,SOC!B:D,2,FALSE)</f>
         <v>1.0017</v>
       </c>
-      <c r="D66" s="18" t="str">
+      <c r="D66" s="17" t="str">
         <f>VLOOKUP(B66,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -3104,11 +2514,11 @@
       <c r="B67" s="5">
         <v>45981</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="11">
         <f>VLOOKUP(B67,SOC!B:D,2,FALSE)</f>
         <v>1.0018</v>
       </c>
-      <c r="D67" s="18" t="str">
+      <c r="D67" s="17" t="str">
         <f>VLOOKUP(B67,MCU!B:D,2,FALSE)</f>
         <v>50.05</v>
       </c>
@@ -3125,11 +2535,11 @@
       <c r="B68" s="5">
         <v>46027</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="11">
         <f>VLOOKUP(B68,SOC!B:D,2,FALSE)</f>
         <v>1.002</v>
       </c>
-      <c r="D68" s="18" t="str">
+      <c r="D68" s="17" t="str">
         <f>VLOOKUP(B68,MCU!B:D,2,FALSE)</f>
         <v>50.06</v>
       </c>
@@ -3144,11 +2554,11 @@
       <c r="B69" s="5">
         <v>46041</v>
       </c>
-      <c r="C69" s="12">
+      <c r="C69" s="11">
         <f>VLOOKUP(B69,SOC!B:D,2,FALSE)</f>
         <v>1.0021</v>
       </c>
-      <c r="D69" s="18" t="str">
+      <c r="D69" s="17" t="str">
         <f>VLOOKUP(B69,MCU!B:D,2,FALSE)</f>
         <v>50.06</v>
       </c>
@@ -3162,11 +2572,11 @@
       <c r="B70" s="5">
         <v>46048</v>
       </c>
-      <c r="C70" s="12">
+      <c r="C70" s="11">
         <f>VLOOKUP(B70,SOC!B:D,2,FALSE)</f>
         <v>1.0021</v>
       </c>
-      <c r="D70" s="18" t="str">
+      <c r="D70" s="17" t="str">
         <f>VLOOKUP(B70,MCU!B:D,2,FALSE)</f>
         <v>50.06</v>
       </c>
@@ -3183,11 +2593,11 @@
       <c r="B71" s="5">
         <v>46066</v>
       </c>
-      <c r="C71" s="12">
+      <c r="C71" s="11">
         <f>VLOOKUP(B71,SOC!B:D,2,FALSE)</f>
         <v>1.0022</v>
       </c>
-      <c r="D71" s="18" t="str">
+      <c r="D71" s="17" t="str">
         <f>VLOOKUP(B71,MCU!B:D,2,FALSE)</f>
         <v>50.06</v>
       </c>
@@ -3202,11 +2612,11 @@
       <c r="B72" s="5">
         <v>46125</v>
       </c>
-      <c r="C72" s="12">
+      <c r="C72" s="11">
         <f>VLOOKUP(B72,SOC!B:D,2,FALSE)</f>
         <v>1.0024</v>
       </c>
-      <c r="D72" s="18" t="str">
+      <c r="D72" s="17" t="str">
         <f>VLOOKUP(B72,MCU!B:D,2,FALSE)</f>
         <v>50.06</v>
       </c>
@@ -3219,7 +2629,7 @@
     </row>
     <row r="73" spans="2:7">
       <c r="B73" s="6"/>
-      <c r="C73" s="12"/>
+      <c r="C73" s="11"/>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
       <c r="F73" s="6"/>
@@ -3227,7 +2637,7 @@
     </row>
     <row r="74" spans="2:7">
       <c r="B74" s="6"/>
-      <c r="C74" s="12"/>
+      <c r="C74" s="11"/>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
       <c r="F74" s="6"/>
@@ -3235,7 +2645,7 @@
     </row>
     <row r="75" spans="2:7">
       <c r="B75" s="6"/>
-      <c r="C75" s="12"/>
+      <c r="C75" s="11"/>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
       <c r="F75" s="6"/>
@@ -3243,7 +2653,7 @@
     </row>
     <row r="76" spans="2:7">
       <c r="B76" s="6"/>
-      <c r="C76" s="12"/>
+      <c r="C76" s="11"/>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
       <c r="F76" s="6"/>
@@ -3251,7 +2661,7 @@
     </row>
     <row r="77" spans="2:7">
       <c r="B77" s="6"/>
-      <c r="C77" s="12"/>
+      <c r="C77" s="11"/>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
       <c r="F77" s="6"/>
@@ -3259,7 +2669,7 @@
     </row>
     <row r="78" spans="2:7">
       <c r="B78" s="6"/>
-      <c r="C78" s="12"/>
+      <c r="C78" s="11"/>
       <c r="D78" s="6"/>
       <c r="E78" s="6"/>
       <c r="F78" s="6"/>
@@ -3267,7 +2677,7 @@
     </row>
     <row r="79" spans="2:7">
       <c r="B79" s="6"/>
-      <c r="C79" s="12"/>
+      <c r="C79" s="11"/>
       <c r="D79" s="6"/>
       <c r="E79" s="6"/>
       <c r="F79" s="6"/>
@@ -3275,7 +2685,7 @@
     </row>
     <row r="80" spans="2:7">
       <c r="B80" s="6"/>
-      <c r="C80" s="12"/>
+      <c r="C80" s="11"/>
       <c r="D80" s="6"/>
       <c r="E80" s="6"/>
       <c r="F80" s="6"/>
@@ -3283,7 +2693,7 @@
     </row>
     <row r="81" spans="2:7">
       <c r="B81" s="6"/>
-      <c r="C81" s="12"/>
+      <c r="C81" s="11"/>
       <c r="D81" s="6"/>
       <c r="E81" s="6"/>
       <c r="F81" s="6"/>
@@ -3291,7 +2701,7 @@
     </row>
     <row r="82" spans="2:7">
       <c r="B82" s="6"/>
-      <c r="C82" s="12"/>
+      <c r="C82" s="11"/>
       <c r="D82" s="6"/>
       <c r="E82" s="6"/>
       <c r="F82" s="6"/>
@@ -3299,7 +2709,7 @@
     </row>
     <row r="83" spans="2:7">
       <c r="B83" s="6"/>
-      <c r="C83" s="12"/>
+      <c r="C83" s="11"/>
       <c r="D83" s="6"/>
       <c r="E83" s="6"/>
       <c r="F83" s="6"/>
@@ -3307,7 +2717,7 @@
     </row>
     <row r="84" spans="2:7">
       <c r="B84" s="6"/>
-      <c r="C84" s="12"/>
+      <c r="C84" s="11"/>
       <c r="D84" s="6"/>
       <c r="E84" s="6"/>
       <c r="F84" s="6"/>
@@ -3315,7 +2725,7 @@
     </row>
     <row r="85" spans="2:7">
       <c r="B85" s="6"/>
-      <c r="C85" s="12"/>
+      <c r="C85" s="11"/>
       <c r="D85" s="6"/>
       <c r="E85" s="6"/>
       <c r="F85" s="6"/>
@@ -3323,7 +2733,7 @@
     </row>
     <row r="86" spans="2:7">
       <c r="B86" s="6"/>
-      <c r="C86" s="12"/>
+      <c r="C86" s="11"/>
       <c r="D86" s="6"/>
       <c r="E86" s="6"/>
       <c r="F86" s="6"/>
@@ -3331,24 +2741,23 @@
     </row>
     <row r="87" spans="2:7">
       <c r="B87" s="6"/>
-      <c r="C87" s="12"/>
+      <c r="C87" s="11"/>
       <c r="D87" s="6"/>
       <c r="E87" s="6"/>
       <c r="F87" s="6"/>
       <c r="G87" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B3:D91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="29.75" customWidth="1"/>
@@ -3370,8 +2779,8 @@
         <f>統合ソフト!B4</f>
         <v>45170</v>
       </c>
-      <c r="C4" s="12">
-        <v>0.00011</v>
+      <c r="C4" s="11">
+        <v>1.1E-4</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>37</v>
@@ -3381,8 +2790,8 @@
       <c r="B5" s="5">
         <v>45225</v>
       </c>
-      <c r="C5" s="12">
-        <v>0.02041</v>
+      <c r="C5" s="11">
+        <v>2.0410000000000001E-2</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>38</v>
@@ -3392,8 +2801,8 @@
       <c r="B6" s="5">
         <v>45229</v>
       </c>
-      <c r="C6" s="12">
-        <v>0.02046</v>
+      <c r="C6" s="11">
+        <v>2.0459999999999999E-2</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>39</v>
@@ -3403,19 +2812,19 @@
       <c r="B7" s="5">
         <v>45231</v>
       </c>
-      <c r="C7" s="12">
-        <v>0.02051</v>
+      <c r="C7" s="11">
+        <v>2.051E-2</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" ht="28.5" spans="2:4">
+    <row r="8" spans="2:4" ht="28.5">
       <c r="B8" s="5">
         <v>45244</v>
       </c>
-      <c r="C8" s="12">
-        <v>0.0207</v>
+      <c r="C8" s="11">
+        <v>2.07E-2</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>41</v>
@@ -3425,8 +2834,8 @@
       <c r="B9" s="5">
         <v>45271</v>
       </c>
-      <c r="C9" s="12">
-        <v>0.03016</v>
+      <c r="C9" s="11">
+        <v>3.0159999999999999E-2</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>42</v>
@@ -3436,8 +2845,8 @@
       <c r="B10" s="5">
         <v>45279</v>
       </c>
-      <c r="C10" s="12">
-        <v>0.0303</v>
+      <c r="C10" s="11">
+        <v>3.0300000000000001E-2</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>43</v>
@@ -3447,8 +2856,8 @@
       <c r="B11" s="5">
         <v>45282</v>
       </c>
-      <c r="C11" s="12">
-        <v>0.030331</v>
+      <c r="C11" s="11">
+        <v>3.0331E-2</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>44</v>
@@ -3458,8 +2867,8 @@
       <c r="B12" s="5">
         <v>45306</v>
       </c>
-      <c r="C12" s="12">
-        <v>0.03066</v>
+      <c r="C12" s="11">
+        <v>3.066E-2</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>45</v>
@@ -3469,19 +2878,19 @@
       <c r="B13" s="5">
         <v>45348</v>
       </c>
-      <c r="C13" s="12">
-        <v>0.03126</v>
+      <c r="C13" s="11">
+        <v>3.1260000000000003E-2</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="14" ht="28.5" spans="2:4">
+    <row r="14" spans="2:4" ht="28.5">
       <c r="B14" s="5">
         <v>45357</v>
       </c>
-      <c r="C14" s="12">
-        <v>0.031261</v>
+      <c r="C14" s="11">
+        <v>3.1260999999999997E-2</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>47</v>
@@ -3491,8 +2900,8 @@
       <c r="B15" s="5">
         <v>45369</v>
       </c>
-      <c r="C15" s="12">
-        <v>0.03156</v>
+      <c r="C15" s="11">
+        <v>3.1559999999999998E-2</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>48</v>
@@ -3502,8 +2911,8 @@
       <c r="B16" s="5">
         <v>45383</v>
       </c>
-      <c r="C16" s="12">
-        <v>0.0317</v>
+      <c r="C16" s="11">
+        <v>3.1699999999999999E-2</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>49</v>
@@ -3513,8 +2922,8 @@
       <c r="B17" s="5">
         <v>45397</v>
       </c>
-      <c r="C17" s="12">
-        <v>0.0319</v>
+      <c r="C17" s="11">
+        <v>3.1899999999999998E-2</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>50</v>
@@ -3524,8 +2933,8 @@
       <c r="B18" s="5">
         <v>45406</v>
       </c>
-      <c r="C18" s="12">
-        <v>0.03203</v>
+      <c r="C18" s="11">
+        <v>3.2030000000000003E-2</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>51</v>
@@ -3535,8 +2944,8 @@
       <c r="B19" s="5">
         <v>45406</v>
       </c>
-      <c r="C19" s="12">
-        <v>0.032031</v>
+      <c r="C19" s="11">
+        <v>3.2030999999999997E-2</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>52</v>
@@ -3546,8 +2955,8 @@
       <c r="B20" s="5">
         <v>45411</v>
       </c>
-      <c r="C20" s="12">
-        <v>0.0321</v>
+      <c r="C20" s="11">
+        <v>3.2099999999999997E-2</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>53</v>
@@ -3557,7 +2966,7 @@
       <c r="B21" s="5">
         <v>45432</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="11">
         <v>0.04</v>
       </c>
       <c r="D21" s="6" t="s">
@@ -3568,8 +2977,8 @@
       <c r="B22" s="5">
         <v>45446</v>
       </c>
-      <c r="C22" s="12">
-        <v>0.0402</v>
+      <c r="C22" s="11">
+        <v>4.02E-2</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>55</v>
@@ -3579,8 +2988,8 @@
       <c r="B23" s="5">
         <v>45460</v>
       </c>
-      <c r="C23" s="12">
-        <v>0.0404</v>
+      <c r="C23" s="11">
+        <v>4.0399999999999998E-2</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>56</v>
@@ -3590,8 +2999,8 @@
       <c r="B24" s="5">
         <v>45474</v>
       </c>
-      <c r="C24" s="12">
-        <v>0.0406</v>
+      <c r="C24" s="11">
+        <v>4.0599999999999997E-2</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>57</v>
@@ -3601,8 +3010,8 @@
       <c r="B25" s="5">
         <v>45488</v>
       </c>
-      <c r="C25" s="12">
-        <v>0.0408</v>
+      <c r="C25" s="11">
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>58</v>
@@ -3612,7 +3021,7 @@
       <c r="B26" s="5">
         <v>45492</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>59</v>
       </c>
       <c r="D26" s="6"/>
@@ -3621,8 +3030,8 @@
       <c r="B27" s="5">
         <v>45502</v>
       </c>
-      <c r="C27" s="12">
-        <v>0.041</v>
+      <c r="C27" s="11">
+        <v>4.1000000000000002E-2</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>60</v>
@@ -3632,8 +3041,8 @@
       <c r="B28" s="5">
         <v>45510</v>
       </c>
-      <c r="C28" s="12">
-        <v>0.0411</v>
+      <c r="C28" s="11">
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="D28" s="7" t="s">
         <v>61</v>
@@ -3643,8 +3052,8 @@
       <c r="B29" s="5">
         <v>45523</v>
       </c>
-      <c r="C29" s="12">
-        <v>0.0413</v>
+      <c r="C29" s="11">
+        <v>4.1300000000000003E-2</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>62</v>
@@ -3654,8 +3063,8 @@
       <c r="B30" s="5">
         <v>45534</v>
       </c>
-      <c r="C30" s="12">
-        <v>0.0411</v>
+      <c r="C30" s="11">
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>63</v>
@@ -3665,8 +3074,8 @@
       <c r="B31" s="5">
         <v>45537</v>
       </c>
-      <c r="C31" s="12">
-        <v>0.0415</v>
+      <c r="C31" s="11">
+        <v>4.1500000000000002E-2</v>
       </c>
       <c r="D31" s="7" t="s">
         <v>64</v>
@@ -3676,8 +3085,8 @@
       <c r="B32" s="5">
         <v>45553</v>
       </c>
-      <c r="C32" s="12">
-        <v>0.0417</v>
+      <c r="C32" s="11">
+        <v>4.1700000000000001E-2</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>65</v>
@@ -3687,8 +3096,8 @@
       <c r="B33" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C33" s="12">
-        <v>0.04171</v>
+      <c r="C33" s="11">
+        <v>4.1709999999999997E-2</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>65</v>
@@ -3698,8 +3107,8 @@
       <c r="B34" s="5">
         <v>45554</v>
       </c>
-      <c r="C34" s="12">
-        <v>0.0417</v>
+      <c r="C34" s="11">
+        <v>4.1700000000000001E-2</v>
       </c>
       <c r="D34" s="7" t="s">
         <v>66</v>
@@ -3709,8 +3118,8 @@
       <c r="B35" s="5">
         <v>45555</v>
       </c>
-      <c r="C35" s="12">
-        <v>0.0411</v>
+      <c r="C35" s="11">
+        <v>4.1099999999999998E-2</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>67</v>
@@ -3720,8 +3129,8 @@
       <c r="B36" s="5">
         <v>45564</v>
       </c>
-      <c r="C36" s="12">
-        <v>0.0419</v>
+      <c r="C36" s="11">
+        <v>4.19E-2</v>
       </c>
       <c r="D36" s="7" t="s">
         <v>68</v>
@@ -3731,8 +3140,8 @@
       <c r="B37" s="5">
         <v>45579</v>
       </c>
-      <c r="C37" s="12">
-        <v>0.0421</v>
+      <c r="C37" s="11">
+        <v>4.2099999999999999E-2</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>69</v>
@@ -3742,7 +3151,7 @@
       <c r="B38" s="5">
         <v>45593</v>
       </c>
-      <c r="C38" s="12">
+      <c r="C38" s="11">
         <v>0.05</v>
       </c>
       <c r="D38" s="6" t="s">
@@ -3753,8 +3162,8 @@
       <c r="B39" s="5">
         <v>45607</v>
       </c>
-      <c r="C39" s="12">
-        <v>0.0503</v>
+      <c r="C39" s="11">
+        <v>5.0299999999999997E-2</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>71</v>
@@ -3764,8 +3173,8 @@
       <c r="B40" s="5">
         <v>45621</v>
       </c>
-      <c r="C40" s="12">
-        <v>0.0505</v>
+      <c r="C40" s="11">
+        <v>5.0500000000000003E-2</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>72</v>
@@ -3775,8 +3184,8 @@
       <c r="B41" s="5">
         <v>45637</v>
       </c>
-      <c r="C41" s="12">
-        <v>0.0507</v>
+      <c r="C41" s="11">
+        <v>5.0700000000000002E-2</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>73</v>
@@ -3786,8 +3195,8 @@
       <c r="B42" s="5">
         <v>45660</v>
       </c>
-      <c r="C42" s="12">
-        <v>0.0511</v>
+      <c r="C42" s="11">
+        <v>5.11E-2</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>74</v>
@@ -3797,8 +3206,8 @@
       <c r="B43" s="5">
         <v>45679</v>
       </c>
-      <c r="C43" s="12">
-        <v>0.0513</v>
+      <c r="C43" s="11">
+        <v>5.1299999999999998E-2</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>75</v>
@@ -3808,8 +3217,8 @@
       <c r="B44" s="5">
         <v>45698</v>
       </c>
-      <c r="C44" s="12">
-        <v>0.0516</v>
+      <c r="C44" s="11">
+        <v>5.16E-2</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>76</v>
@@ -3819,8 +3228,8 @@
       <c r="B45" s="5">
         <v>45707</v>
       </c>
-      <c r="C45" s="12">
-        <v>0.0517</v>
+      <c r="C45" s="11">
+        <v>5.1700000000000003E-2</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>77</v>
@@ -3830,7 +3239,7 @@
       <c r="B46" s="5">
         <v>45719</v>
       </c>
-      <c r="C46" s="12">
+      <c r="C46" s="11">
         <v>1</v>
       </c>
       <c r="D46" s="6" t="s">
@@ -3841,7 +3250,7 @@
       <c r="B47" s="5">
         <v>45733</v>
       </c>
-      <c r="C47" s="12">
+      <c r="C47" s="11">
         <v>1.0001</v>
       </c>
       <c r="D47" s="6" t="s">
@@ -3852,7 +3261,7 @@
       <c r="B48" s="5">
         <v>45754</v>
       </c>
-      <c r="C48" s="12">
+      <c r="C48" s="11">
         <v>1.0002</v>
       </c>
       <c r="D48" s="6" t="s">
@@ -3863,7 +3272,7 @@
       <c r="B49" s="5">
         <v>45761</v>
       </c>
-      <c r="C49" s="12">
+      <c r="C49" s="11">
         <v>1.0003</v>
       </c>
       <c r="D49" s="6" t="s">
@@ -3874,7 +3283,7 @@
       <c r="B50" s="5">
         <v>45777</v>
       </c>
-      <c r="C50" s="12">
+      <c r="C50" s="11">
         <v>1.0004</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -3885,8 +3294,8 @@
       <c r="B51" s="5">
         <v>45786</v>
       </c>
-      <c r="C51" s="12">
-        <v>1.0006</v>
+      <c r="C51" s="11">
+        <v>1.0005999999999999</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>83</v>
@@ -3896,8 +3305,8 @@
       <c r="B52" s="5">
         <v>45797</v>
       </c>
-      <c r="C52" s="12">
-        <v>1.0006</v>
+      <c r="C52" s="11">
+        <v>1.0005999999999999</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>84</v>
@@ -3907,8 +3316,8 @@
       <c r="B53" s="5">
         <v>45803</v>
       </c>
-      <c r="C53" s="12">
-        <v>1.0008</v>
+      <c r="C53" s="11">
+        <v>1.0007999999999999</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>85</v>
@@ -3918,8 +3327,8 @@
       <c r="B54" s="5">
         <v>45825</v>
       </c>
-      <c r="C54" s="12">
-        <v>1.0009</v>
+      <c r="C54" s="11">
+        <v>1.0008999999999999</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>86</v>
@@ -3929,8 +3338,8 @@
       <c r="B55" s="5">
         <v>45826</v>
       </c>
-      <c r="C55" s="12">
-        <v>1.001</v>
+      <c r="C55" s="11">
+        <v>1.0009999999999999</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>86</v>
@@ -3940,8 +3349,8 @@
       <c r="B56" s="5">
         <v>45838</v>
       </c>
-      <c r="C56" s="12">
-        <v>1.0011</v>
+      <c r="C56" s="11">
+        <v>1.0011000000000001</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>87</v>
@@ -3951,8 +3360,8 @@
       <c r="B57" s="5">
         <v>45854</v>
       </c>
-      <c r="C57" s="12">
-        <v>1.0012</v>
+      <c r="C57" s="11">
+        <v>1.0012000000000001</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>88</v>
@@ -3962,8 +3371,8 @@
       <c r="B58" s="5">
         <v>45859</v>
       </c>
-      <c r="C58" s="12">
-        <v>1.0013</v>
+      <c r="C58" s="11">
+        <v>1.0013000000000001</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>88</v>
@@ -3973,8 +3382,8 @@
       <c r="B59" s="5">
         <v>45884</v>
       </c>
-      <c r="C59" s="12">
-        <v>1.0014</v>
+      <c r="C59" s="11">
+        <v>1.0014000000000001</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>89</v>
@@ -3984,8 +3393,8 @@
       <c r="B60" s="5">
         <v>45915</v>
       </c>
-      <c r="C60" s="12">
-        <v>1.0015</v>
+      <c r="C60" s="11">
+        <v>1.0015000000000001</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>90</v>
@@ -3995,7 +3404,7 @@
       <c r="B61" s="5">
         <v>45944</v>
       </c>
-      <c r="C61" s="12">
+      <c r="C61" s="11">
         <v>1.0016</v>
       </c>
       <c r="D61" s="6" t="s">
@@ -4006,7 +3415,7 @@
       <c r="B62" s="5">
         <v>45950</v>
       </c>
-      <c r="C62" s="12">
+      <c r="C62" s="11">
         <v>1.0017</v>
       </c>
       <c r="D62" s="6" t="s">
@@ -4017,7 +3426,7 @@
       <c r="B63" s="5">
         <v>45981</v>
       </c>
-      <c r="C63" s="12">
+      <c r="C63" s="11">
         <v>1.0018</v>
       </c>
       <c r="D63" s="6" t="s">
@@ -4028,7 +3437,7 @@
       <c r="B64" s="5">
         <v>46027</v>
       </c>
-      <c r="C64" s="12">
+      <c r="C64" s="11">
         <v>1.002</v>
       </c>
       <c r="D64" s="6" t="s">
@@ -4039,7 +3448,7 @@
       <c r="B65" s="5">
         <v>46041</v>
       </c>
-      <c r="C65" s="12">
+      <c r="C65" s="11">
         <v>1.0021</v>
       </c>
       <c r="D65" s="6" t="s">
@@ -4050,7 +3459,7 @@
       <c r="B66" s="5">
         <v>46048</v>
       </c>
-      <c r="C66" s="12">
+      <c r="C66" s="11">
         <v>1.0021</v>
       </c>
       <c r="D66" s="6" t="s">
@@ -4061,7 +3470,7 @@
       <c r="B67" s="5">
         <v>46066</v>
       </c>
-      <c r="C67" s="12">
+      <c r="C67" s="11">
         <v>1.0022</v>
       </c>
       <c r="D67" s="6" t="s">
@@ -4072,7 +3481,7 @@
       <c r="B68" s="5">
         <v>46125</v>
       </c>
-      <c r="C68" s="12">
+      <c r="C68" s="11">
         <v>1.0024</v>
       </c>
       <c r="D68" s="6" t="s">
@@ -4081,130 +3490,129 @@
     </row>
     <row r="69" spans="2:4">
       <c r="B69" s="6"/>
-      <c r="C69" s="12"/>
+      <c r="C69" s="11"/>
       <c r="D69" s="6"/>
     </row>
     <row r="70" spans="2:4">
       <c r="B70" s="6"/>
-      <c r="C70" s="12"/>
+      <c r="C70" s="11"/>
       <c r="D70" s="6"/>
     </row>
     <row r="71" spans="2:4">
       <c r="B71" s="6"/>
-      <c r="C71" s="12"/>
+      <c r="C71" s="11"/>
       <c r="D71" s="6"/>
     </row>
     <row r="72" spans="2:4">
       <c r="B72" s="6"/>
-      <c r="C72" s="12"/>
+      <c r="C72" s="11"/>
       <c r="D72" s="6"/>
     </row>
     <row r="73" spans="2:4">
       <c r="B73" s="6"/>
-      <c r="C73" s="12"/>
+      <c r="C73" s="11"/>
       <c r="D73" s="6"/>
     </row>
     <row r="74" spans="2:4">
       <c r="B74" s="6"/>
-      <c r="C74" s="12"/>
+      <c r="C74" s="11"/>
       <c r="D74" s="6"/>
     </row>
     <row r="75" spans="2:4">
       <c r="B75" s="6"/>
-      <c r="C75" s="12"/>
+      <c r="C75" s="11"/>
       <c r="D75" s="6"/>
     </row>
     <row r="76" spans="2:4">
       <c r="B76" s="6"/>
-      <c r="C76" s="12"/>
+      <c r="C76" s="11"/>
       <c r="D76" s="6"/>
     </row>
     <row r="77" spans="2:4">
       <c r="B77" s="6"/>
-      <c r="C77" s="12"/>
+      <c r="C77" s="11"/>
       <c r="D77" s="6"/>
     </row>
     <row r="78" spans="2:4">
       <c r="B78" s="6"/>
-      <c r="C78" s="12"/>
+      <c r="C78" s="11"/>
       <c r="D78" s="6"/>
     </row>
     <row r="79" spans="2:4">
       <c r="B79" s="6"/>
-      <c r="C79" s="12"/>
+      <c r="C79" s="11"/>
       <c r="D79" s="6"/>
     </row>
     <row r="80" spans="2:4">
       <c r="B80" s="6"/>
-      <c r="C80" s="12"/>
+      <c r="C80" s="11"/>
       <c r="D80" s="6"/>
     </row>
     <row r="81" spans="2:4">
       <c r="B81" s="6"/>
-      <c r="C81" s="12"/>
+      <c r="C81" s="11"/>
       <c r="D81" s="6"/>
     </row>
     <row r="82" spans="2:4">
       <c r="B82" s="6"/>
-      <c r="C82" s="12"/>
+      <c r="C82" s="11"/>
       <c r="D82" s="6"/>
     </row>
     <row r="83" spans="2:4">
       <c r="B83" s="6"/>
-      <c r="C83" s="12"/>
+      <c r="C83" s="11"/>
       <c r="D83" s="6"/>
     </row>
     <row r="84" spans="2:4">
       <c r="B84" s="6"/>
-      <c r="C84" s="12"/>
+      <c r="C84" s="11"/>
       <c r="D84" s="6"/>
     </row>
     <row r="85" spans="2:4">
       <c r="B85" s="6"/>
-      <c r="C85" s="12"/>
+      <c r="C85" s="11"/>
       <c r="D85" s="6"/>
     </row>
     <row r="86" spans="2:4">
       <c r="B86" s="6"/>
-      <c r="C86" s="12"/>
+      <c r="C86" s="11"/>
       <c r="D86" s="6"/>
     </row>
     <row r="87" spans="2:4">
       <c r="B87" s="6"/>
-      <c r="C87" s="12"/>
+      <c r="C87" s="11"/>
       <c r="D87" s="6"/>
     </row>
     <row r="88" spans="2:4">
       <c r="B88" s="6"/>
-      <c r="C88" s="12"/>
+      <c r="C88" s="11"/>
       <c r="D88" s="6"/>
     </row>
     <row r="89" spans="2:4">
       <c r="B89" s="6"/>
-      <c r="C89" s="12"/>
+      <c r="C89" s="11"/>
       <c r="D89" s="6"/>
     </row>
     <row r="90" spans="2:4">
       <c r="B90" s="6"/>
-      <c r="C90" s="12"/>
+      <c r="C90" s="11"/>
       <c r="D90" s="6"/>
     </row>
     <row r="91" spans="2:4">
       <c r="B91" s="6"/>
-      <c r="C91" s="12"/>
+      <c r="C91" s="11"/>
       <c r="D91" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B3:D91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="3" width="11" customWidth="1"/>
     <col min="4" max="4" width="27" customWidth="1"/>
@@ -4226,18 +3634,18 @@
         <f>統合ソフト!B4</f>
         <v>45170</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="18" t="s">
         <v>99</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="5" ht="57" spans="2:4">
+    <row r="5" spans="2:4" ht="57">
       <c r="B5" s="5">
         <v>45230</v>
       </c>
-      <c r="C5" s="18" t="s">
+      <c r="C5" s="17" t="s">
         <v>100</v>
       </c>
       <c r="D5" s="7" t="s">
@@ -4248,18 +3656,18 @@
       <c r="B6" s="5">
         <v>45236</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="18" t="s">
         <v>99</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="7" ht="28.5" spans="2:4">
+    <row r="7" spans="2:4" ht="28.5">
       <c r="B7" s="5">
         <v>45244</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="17" t="s">
         <v>103</v>
       </c>
       <c r="D7" s="7" t="s">
@@ -4270,18 +3678,18 @@
       <c r="B8" s="5">
         <v>45250</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="17" t="s">
         <v>104</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="9" ht="28.5" spans="2:4">
+    <row r="9" spans="2:4" ht="28.5">
       <c r="B9" s="5">
         <v>45264</v>
       </c>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="17" t="s">
         <v>106</v>
       </c>
       <c r="D9" s="7" t="s">
@@ -4292,7 +3700,7 @@
       <c r="B10" s="5">
         <v>45271</v>
       </c>
-      <c r="C10" s="18" t="s">
+      <c r="C10" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D10" s="6" t="s">
@@ -4303,7 +3711,7 @@
       <c r="B11" s="5">
         <v>45279</v>
       </c>
-      <c r="C11" s="18" t="s">
+      <c r="C11" s="17" t="s">
         <v>109</v>
       </c>
       <c r="D11" s="6" t="s">
@@ -4314,7 +3722,7 @@
       <c r="B12" s="5">
         <v>45306</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="17" t="s">
         <v>111</v>
       </c>
       <c r="D12" s="6" t="s">
@@ -4325,7 +3733,7 @@
       <c r="B13" s="5">
         <v>45348</v>
       </c>
-      <c r="C13" s="18" t="s">
+      <c r="C13" s="17" t="s">
         <v>112</v>
       </c>
       <c r="D13" s="7" t="s">
@@ -4336,7 +3744,7 @@
       <c r="B14" s="5">
         <v>45369</v>
       </c>
-      <c r="C14" s="18" t="s">
+      <c r="C14" s="17" t="s">
         <v>113</v>
       </c>
       <c r="D14" s="6" t="s">
@@ -4347,7 +3755,7 @@
       <c r="B15" s="5">
         <v>45383</v>
       </c>
-      <c r="C15" s="18" t="s">
+      <c r="C15" s="17" t="s">
         <v>114</v>
       </c>
       <c r="D15" s="6" t="s">
@@ -4358,7 +3766,7 @@
       <c r="B16" s="5">
         <v>45397</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="17" t="s">
         <v>115</v>
       </c>
       <c r="D16" s="6" t="s">
@@ -4369,7 +3777,7 @@
       <c r="B17" s="5">
         <v>45407</v>
       </c>
-      <c r="C17" s="18" t="s">
+      <c r="C17" s="17" t="s">
         <v>116</v>
       </c>
       <c r="D17" s="6" t="s">
@@ -4380,7 +3788,7 @@
       <c r="B18" s="5">
         <v>45411</v>
       </c>
-      <c r="C18" s="18" t="s">
+      <c r="C18" s="17" t="s">
         <v>118</v>
       </c>
       <c r="D18" s="6" t="s">
@@ -4391,7 +3799,7 @@
       <c r="B19" s="5">
         <v>45432</v>
       </c>
-      <c r="C19" s="18" t="s">
+      <c r="C19" s="17" t="s">
         <v>119</v>
       </c>
       <c r="D19" s="6" t="s">
@@ -4402,7 +3810,7 @@
       <c r="B20" s="5">
         <v>45446</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="17" t="s">
         <v>120</v>
       </c>
       <c r="D20" s="6" t="s">
@@ -4413,7 +3821,7 @@
       <c r="B21" s="5">
         <v>45460</v>
       </c>
-      <c r="C21" s="18" t="s">
+      <c r="C21" s="17" t="s">
         <v>121</v>
       </c>
       <c r="D21" s="6" t="s">
@@ -4424,7 +3832,7 @@
       <c r="B22" s="5">
         <v>45474</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="C22" s="17" t="s">
         <v>122</v>
       </c>
       <c r="D22" s="6" t="s">
@@ -4435,7 +3843,7 @@
       <c r="B23" s="5">
         <v>45488</v>
       </c>
-      <c r="C23" s="18" t="s">
+      <c r="C23" s="17" t="s">
         <v>123</v>
       </c>
       <c r="D23" s="6" t="s">
@@ -4455,7 +3863,7 @@
       <c r="B25" s="5">
         <v>45502</v>
       </c>
-      <c r="C25" s="18" t="s">
+      <c r="C25" s="17" t="s">
         <v>125</v>
       </c>
       <c r="D25" s="6" t="s">
@@ -4471,11 +3879,11 @@
       </c>
       <c r="D26" s="6"/>
     </row>
-    <row r="27" ht="28.5" spans="2:4">
+    <row r="27" spans="2:4" ht="28.5">
       <c r="B27" s="5">
         <v>45523</v>
       </c>
-      <c r="C27" s="18" t="s">
+      <c r="C27" s="17" t="s">
         <v>126</v>
       </c>
       <c r="D27" s="7" t="s">
@@ -4486,7 +3894,7 @@
       <c r="B28" s="5">
         <v>45534</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="17" t="s">
         <v>128</v>
       </c>
       <c r="D28" s="6" t="s">
@@ -4497,7 +3905,7 @@
       <c r="B29" s="5">
         <v>45537</v>
       </c>
-      <c r="C29" s="18" t="s">
+      <c r="C29" s="17" t="s">
         <v>129</v>
       </c>
       <c r="D29" s="7" t="s">
@@ -4508,7 +3916,7 @@
       <c r="B30" s="5">
         <v>45553</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="17" t="s">
         <v>130</v>
       </c>
       <c r="D30" s="6" t="s">
@@ -4519,7 +3927,7 @@
       <c r="B31" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="18" t="s">
+      <c r="C31" s="17" t="s">
         <v>130</v>
       </c>
       <c r="D31" s="6" t="s">
@@ -4530,7 +3938,7 @@
       <c r="B32" s="5">
         <v>45554</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="17" t="s">
         <v>131</v>
       </c>
       <c r="D32" s="7" t="s">
@@ -4541,7 +3949,7 @@
       <c r="B33" s="5">
         <v>45555</v>
       </c>
-      <c r="C33" s="18" t="s">
+      <c r="C33" s="17" t="s">
         <v>132</v>
       </c>
       <c r="D33" s="6" t="s">
@@ -4552,7 +3960,7 @@
       <c r="B34" s="5">
         <v>45564</v>
       </c>
-      <c r="C34" s="18" t="s">
+      <c r="C34" s="17" t="s">
         <v>133</v>
       </c>
       <c r="D34" s="7" t="s">
@@ -4563,7 +3971,7 @@
       <c r="B35" s="5">
         <v>45579</v>
       </c>
-      <c r="C35" s="18" t="s">
+      <c r="C35" s="17" t="s">
         <v>134</v>
       </c>
       <c r="D35" s="6" t="s">
@@ -4574,7 +3982,7 @@
       <c r="B36" s="5">
         <v>45593</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="17" t="s">
         <v>135</v>
       </c>
       <c r="D36" s="6" t="s">
@@ -4585,7 +3993,7 @@
       <c r="B37" s="5">
         <v>45607</v>
       </c>
-      <c r="C37" s="18" t="s">
+      <c r="C37" s="17" t="s">
         <v>136</v>
       </c>
       <c r="D37" s="6" t="s">
@@ -4596,7 +4004,7 @@
       <c r="B38" s="5">
         <v>45621</v>
       </c>
-      <c r="C38" s="18" t="s">
+      <c r="C38" s="17" t="s">
         <v>137</v>
       </c>
       <c r="D38" s="6" t="s">
@@ -4607,7 +4015,7 @@
       <c r="B39" s="5">
         <v>45637</v>
       </c>
-      <c r="C39" s="18" t="s">
+      <c r="C39" s="17" t="s">
         <v>138</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -4618,7 +4026,7 @@
       <c r="B40" s="5">
         <v>45660</v>
       </c>
-      <c r="C40" s="18" t="s">
+      <c r="C40" s="17" t="s">
         <v>139</v>
       </c>
       <c r="D40" s="6" t="s">
@@ -4629,7 +4037,7 @@
       <c r="B41" s="5">
         <v>45679</v>
       </c>
-      <c r="C41" s="18" t="s">
+      <c r="C41" s="17" t="s">
         <v>140</v>
       </c>
       <c r="D41" s="6" t="s">
@@ -4640,7 +4048,7 @@
       <c r="B42" s="5">
         <v>45698</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="17" t="s">
         <v>141</v>
       </c>
       <c r="D42" s="6" t="s">
@@ -4651,7 +4059,7 @@
       <c r="B43" s="5">
         <v>45707</v>
       </c>
-      <c r="C43" s="18" t="s">
+      <c r="C43" s="17" t="s">
         <v>142</v>
       </c>
       <c r="D43" s="6" t="s">
@@ -4662,7 +4070,7 @@
       <c r="B44" s="5">
         <v>45719</v>
       </c>
-      <c r="C44" s="18" t="s">
+      <c r="C44" s="17" t="s">
         <v>143</v>
       </c>
       <c r="D44" s="6" t="s">
@@ -4673,7 +4081,7 @@
       <c r="B45" s="5">
         <v>45733</v>
       </c>
-      <c r="C45" s="18" t="s">
+      <c r="C45" s="17" t="s">
         <v>144</v>
       </c>
       <c r="D45" s="6" t="s">
@@ -4684,7 +4092,7 @@
       <c r="B46" s="5">
         <v>45754</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="17" t="s">
         <v>144</v>
       </c>
       <c r="D46" s="6" t="s">
@@ -4695,7 +4103,7 @@
       <c r="B47" s="5">
         <v>45761</v>
       </c>
-      <c r="C47" s="18" t="s">
+      <c r="C47" s="17" t="s">
         <v>145</v>
       </c>
       <c r="D47" s="6" t="s">
@@ -4706,7 +4114,7 @@
       <c r="B48" s="5">
         <v>45777</v>
       </c>
-      <c r="C48" s="18" t="s">
+      <c r="C48" s="17" t="s">
         <v>146</v>
       </c>
       <c r="D48" s="6" t="s">
@@ -4717,7 +4125,7 @@
       <c r="B49" s="5">
         <v>45786</v>
       </c>
-      <c r="C49" s="18" t="s">
+      <c r="C49" s="17" t="s">
         <v>146</v>
       </c>
       <c r="D49" s="6" t="s">
@@ -4728,7 +4136,7 @@
       <c r="B50" s="5">
         <v>45797</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="17" t="s">
         <v>146</v>
       </c>
       <c r="D50" s="6" t="s">
@@ -4739,7 +4147,7 @@
       <c r="B51" s="5">
         <v>45803</v>
       </c>
-      <c r="C51" s="18" t="s">
+      <c r="C51" s="17" t="s">
         <v>147</v>
       </c>
       <c r="D51" s="6" t="s">
@@ -4750,7 +4158,7 @@
       <c r="B52" s="5">
         <v>45825</v>
       </c>
-      <c r="C52" s="18" t="s">
+      <c r="C52" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D52" s="6" t="s">
@@ -4761,7 +4169,7 @@
       <c r="B53" s="5">
         <v>45826</v>
       </c>
-      <c r="C53" s="18" t="s">
+      <c r="C53" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D53" s="6" t="s">
@@ -4772,7 +4180,7 @@
       <c r="B54" s="5">
         <v>45838</v>
       </c>
-      <c r="C54" s="18" t="s">
+      <c r="C54" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D54" s="6" t="s">
@@ -4783,7 +4191,7 @@
       <c r="B55" s="5">
         <v>45854</v>
       </c>
-      <c r="C55" s="18" t="s">
+      <c r="C55" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D55" s="6" t="s">
@@ -4794,7 +4202,7 @@
       <c r="B56" s="5">
         <v>45859</v>
       </c>
-      <c r="C56" s="18" t="s">
+      <c r="C56" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D56" s="6" t="s">
@@ -4805,7 +4213,7 @@
       <c r="B57" s="5">
         <v>45884</v>
       </c>
-      <c r="C57" s="18" t="s">
+      <c r="C57" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D57" s="6" t="s">
@@ -4816,7 +4224,7 @@
       <c r="B58" s="5">
         <v>45915</v>
       </c>
-      <c r="C58" s="18" t="s">
+      <c r="C58" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D58" s="6" t="s">
@@ -4827,7 +4235,7 @@
       <c r="B59" s="5">
         <v>45944</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D59" s="6" t="s">
@@ -4838,7 +4246,7 @@
       <c r="B60" s="5">
         <v>45950</v>
       </c>
-      <c r="C60" s="18" t="s">
+      <c r="C60" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D60" s="6" t="s">
@@ -4849,7 +4257,7 @@
       <c r="B61" s="5">
         <v>45981</v>
       </c>
-      <c r="C61" s="18" t="s">
+      <c r="C61" s="17" t="s">
         <v>148</v>
       </c>
       <c r="D61" s="6" t="s">
@@ -4860,7 +4268,7 @@
       <c r="B62" s="5">
         <v>46027</v>
       </c>
-      <c r="C62" s="18" t="s">
+      <c r="C62" s="17" t="s">
         <v>149</v>
       </c>
       <c r="D62" s="6" t="s">
@@ -4871,7 +4279,7 @@
       <c r="B63" s="5">
         <v>46041</v>
       </c>
-      <c r="C63" s="18" t="s">
+      <c r="C63" s="17" t="s">
         <v>149</v>
       </c>
       <c r="D63" s="6" t="s">
@@ -4882,7 +4290,7 @@
       <c r="B64" s="5">
         <v>46048</v>
       </c>
-      <c r="C64" s="18" t="s">
+      <c r="C64" s="17" t="s">
         <v>149</v>
       </c>
       <c r="D64" s="6" t="s">
@@ -4893,7 +4301,7 @@
       <c r="B65" s="5">
         <v>46066</v>
       </c>
-      <c r="C65" s="18" t="s">
+      <c r="C65" s="17" t="s">
         <v>149</v>
       </c>
       <c r="D65" s="6" t="s">
@@ -4904,7 +4312,7 @@
       <c r="B66" s="5">
         <v>46125</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="17" t="s">
         <v>149</v>
       </c>
       <c r="D66" s="6" t="s">
@@ -5037,21 +4445,20 @@
       <c r="D91" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B3:E92"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="11" customWidth="1"/>
-    <col min="3" max="3" width="15.0833333333333" customWidth="1"/>
-    <col min="4" max="4" width="18.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="79.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="15.125" customWidth="1"/>
+    <col min="4" max="4" width="18.625" customWidth="1"/>
+    <col min="5" max="5" width="79.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:5">
@@ -5068,7 +4475,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" ht="28.5" spans="2:5">
+    <row r="4" spans="2:5" ht="28.5">
       <c r="B4" s="2">
         <v>45170</v>
       </c>
@@ -5082,7 +4489,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" ht="85.5" spans="2:5">
+    <row r="5" spans="2:5" ht="85.5">
       <c r="B5" s="2">
         <v>45271</v>
       </c>
@@ -5096,7 +4503,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="6" ht="159" customHeight="1" spans="2:5">
+    <row r="6" spans="2:5" ht="159" customHeight="1">
       <c r="B6" s="2">
         <v>45348</v>
       </c>
@@ -5110,7 +4517,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="7" ht="51.75" customHeight="1" spans="2:5">
+    <row r="7" spans="2:5" ht="51.75" customHeight="1">
       <c r="B7" s="2">
         <v>45369</v>
       </c>
@@ -5136,7 +4543,7 @@
       </c>
       <c r="E8" s="3"/>
     </row>
-    <row r="9" ht="71.25" spans="2:5">
+    <row r="9" spans="2:5" ht="71.25">
       <c r="B9" s="2">
         <v>45392</v>
       </c>
@@ -5150,7 +4557,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="10" ht="71.25" spans="2:5">
+    <row r="10" spans="2:5" ht="71.25">
       <c r="B10" s="2">
         <v>45406</v>
       </c>
@@ -5192,7 +4599,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" ht="99.75" spans="2:5">
+    <row r="13" spans="2:5" ht="99.75">
       <c r="B13" s="2">
         <v>45460</v>
       </c>
@@ -5220,7 +4627,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" ht="42.75" spans="2:5">
+    <row r="15" spans="2:5" ht="42.75">
       <c r="B15" s="2">
         <v>45488</v>
       </c>
@@ -5234,7 +4641,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="16" ht="28.5" spans="2:5">
+    <row r="16" spans="2:5" ht="28.5">
       <c r="B16" s="2">
         <v>45492</v>
       </c>
@@ -5276,7 +4683,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="19" ht="28.5" spans="2:5">
+    <row r="19" spans="2:5" ht="28.5">
       <c r="B19" s="2">
         <v>45511</v>
       </c>
@@ -5304,7 +4711,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" ht="28.5" spans="2:5">
+    <row r="21" spans="2:5" ht="28.5">
       <c r="B21" s="8">
         <v>45533</v>
       </c>
@@ -5318,7 +4725,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="22" ht="28.5" spans="2:5">
+    <row r="22" spans="2:5" ht="28.5">
       <c r="B22" s="8">
         <v>45546</v>
       </c>
@@ -5346,7 +4753,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="24" ht="42.75" spans="2:5">
+    <row r="24" spans="2:5" ht="42.75">
       <c r="B24" s="9">
         <v>45593</v>
       </c>
@@ -5374,7 +4781,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="26" ht="42.75" spans="2:5">
+    <row r="26" spans="2:5" ht="42.75">
       <c r="B26" s="8">
         <v>45621</v>
       </c>
@@ -5388,7 +4795,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="27" ht="99.75" spans="2:5">
+    <row r="27" spans="2:5" ht="99.75">
       <c r="B27" s="8">
         <v>45637</v>
       </c>
@@ -5402,7 +4809,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="28" ht="71.25" spans="2:5">
+    <row r="28" spans="2:5" ht="71.25">
       <c r="B28" s="5">
         <v>45719</v>
       </c>
@@ -5416,7 +4823,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="29" ht="71.25" spans="2:5">
+    <row r="29" spans="2:5" ht="71.25">
       <c r="B29" s="5">
         <v>45733</v>
       </c>
@@ -5841,20 +5248,19 @@
       <c r="E92" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:D91"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="53.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="53.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
@@ -5872,29 +5278,29 @@
       <c r="B4" s="2">
         <v>45230</v>
       </c>
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="19" t="s">
         <v>215</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="5" ht="28.5" spans="2:4">
+    <row r="5" spans="2:4" ht="28.5">
       <c r="B5" s="2">
         <v>45271</v>
       </c>
-      <c r="C5" s="20" t="s">
+      <c r="C5" s="19" t="s">
         <v>217</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="6" ht="28.5" spans="2:4">
+    <row r="6" spans="2:4" ht="28.5">
       <c r="B6" s="2">
         <v>45306</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="19" t="s">
         <v>219</v>
       </c>
       <c r="D6" s="4" t="s">
@@ -5905,18 +5311,18 @@
       <c r="B7" s="2">
         <v>45343</v>
       </c>
-      <c r="C7" s="20" t="s">
+      <c r="C7" s="19" t="s">
         <v>221</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="8" ht="42.75" spans="2:4">
+    <row r="8" spans="2:4" ht="42.75">
       <c r="B8" s="2">
         <v>45369</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>223</v>
       </c>
       <c r="D8" s="4" t="s">
@@ -5927,7 +5333,7 @@
       <c r="B9" s="2">
         <v>45383</v>
       </c>
-      <c r="C9" s="20" t="s">
+      <c r="C9" s="19" t="s">
         <v>225</v>
       </c>
       <c r="D9" s="3" t="s">
@@ -5938,7 +5344,7 @@
       <c r="B10" s="2">
         <v>45397</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="19" t="s">
         <v>227</v>
       </c>
       <c r="D10" s="3" t="s">
@@ -5949,29 +5355,29 @@
       <c r="B11" s="2">
         <v>45411</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="19" t="s">
         <v>229</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="12" ht="57" spans="2:4">
+    <row r="12" spans="2:4" ht="57">
       <c r="B12" s="2">
         <v>45432</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="19" t="s">
         <v>231</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="13" ht="28.5" spans="2:4">
+    <row r="13" spans="2:4" ht="28.5">
       <c r="B13" s="2">
         <v>45446</v>
       </c>
-      <c r="C13" s="20" t="s">
+      <c r="C13" s="19" t="s">
         <v>233</v>
       </c>
       <c r="D13" s="4" t="s">
@@ -5982,7 +5388,7 @@
       <c r="B14" s="2">
         <v>45460</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>235</v>
       </c>
       <c r="D14" s="4" t="s">
@@ -5993,7 +5399,7 @@
       <c r="B15" s="2">
         <v>45474</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>236</v>
       </c>
       <c r="D15" s="4" t="s">
@@ -6004,7 +5410,7 @@
       <c r="B16" s="2">
         <v>45488</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="19" t="s">
         <v>235</v>
       </c>
       <c r="D16" s="4" t="s">
@@ -6059,7 +5465,7 @@
       <c r="B21" s="5">
         <v>45564</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="C21" s="19" t="s">
         <v>238</v>
       </c>
       <c r="D21" s="6" t="s">
@@ -6081,7 +5487,7 @@
       <c r="B23" s="5">
         <v>45593</v>
       </c>
-      <c r="C23" s="20" t="s">
+      <c r="C23" s="19" t="s">
         <v>240</v>
       </c>
       <c r="D23" s="6" t="s">
@@ -6092,7 +5498,7 @@
       <c r="B24" s="5">
         <v>45607</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="19" t="s">
         <v>242</v>
       </c>
       <c r="D24" s="6" t="s">
@@ -6154,11 +5560,11 @@
         <v>235</v>
       </c>
     </row>
-    <row r="30" ht="28.5" spans="2:4">
+    <row r="30" spans="2:4" ht="28.5">
       <c r="B30" s="5">
         <v>45777</v>
       </c>
-      <c r="C30" s="18" t="s">
+      <c r="C30" s="17" t="s">
         <v>244</v>
       </c>
       <c r="D30" s="7" t="s">
@@ -6471,7 +5877,7 @@
       <c r="D91" s="6"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>